--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2025.xlsx
@@ -1649,11 +1649,7 @@
           <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>TECNOLOGIA BS SPA</t>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1074,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1139,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1204,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1269,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1334,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1399,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1464,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1529,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1594,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1555,12 +1611,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1260-19-CM25</t>
+          <t>2369-7-SE25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1570,53 +1626,57 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>96.899.890-0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>19852.06</v>
+        <v>413352.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3904-66-CM25</t>
+          <t>1260-19-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1636,44 +1696,52 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>20856.82</v>
+        <v>19852.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1260-24-CM25</t>
+          <t>3904-66-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,48 +1761,48 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>I MUNICIPALIDAD DE BULNES</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>33921.9</v>
+        <v>20856.82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3447-308-CM25</t>
+          <t>1260-24-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,97 +1827,170 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8620.549999999999</v>
+        <v>33921.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>3447-308-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ene-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>8620.549999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>1057439-799-CM25</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2239-11-LR24</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>ene-2025</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ene-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>61.606.402-9</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Coquimbo</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
         <v>6556.83</v>
       </c>
     </row>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2025.xlsx
@@ -1774,7 +1774,11 @@
           <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>TECNOLOGIA BS SPA</t>
